--- a/data/CPL_2026_PreAuction_Template.xlsx
+++ b/data/CPL_2026_PreAuction_Template.xlsx
@@ -544,10 +544,10 @@
         <v>Avengers</v>
       </c>
       <c r="B2" t="str">
-        <v>2BJB</v>
+        <v>5DXX</v>
       </c>
       <c r="C2" t="str">
-        <v>Pradeep Kumar Pala</v>
+        <v>Siva Naga Kishore Raju Samanthapudi</v>
       </c>
       <c r="D2" t="str">
         <v>All-rounder</v>
@@ -562,7 +562,7 @@
         <v>Unknown</v>
       </c>
       <c r="H2" t="str">
-        <v>2BJB.jpg</v>
+        <v>5DXX.jpg</v>
       </c>
       <c r="I2" t="str">
         <v>All-rounder</v>
@@ -631,10 +631,10 @@
         <v>Avengers</v>
       </c>
       <c r="B5" t="str">
-        <v>5DXX</v>
+        <v>2BJB</v>
       </c>
       <c r="C5" t="str">
-        <v>Siva Naga Kishore Raju Samanthapudi</v>
+        <v>Pradeep Kumar Pala</v>
       </c>
       <c r="D5" t="str">
         <v>All-rounder</v>
@@ -649,7 +649,7 @@
         <v>Unknown</v>
       </c>
       <c r="H5" t="str">
-        <v>5DXX.jpg</v>
+        <v>2BJB.jpg</v>
       </c>
       <c r="I5" t="str">
         <v>All-rounder</v>
